--- a/리눅스 기초 디비.xlsx
+++ b/리눅스 기초 디비.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CYWELL\Desktop\linux\minitest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CYWELL\Desktop\linux\minitest\linux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF369F4-5B32-4EBF-9997-D273A09265AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B78BD81-4D3E-4FE3-BE1E-B952E1567954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11292" yWindow="204" windowWidth="11028" windowHeight="12036" firstSheet="3" activeTab="5" xr2:uid="{E72E1A8E-89CC-47CA-9DAD-E09CE3761029}"/>
+    <workbookView xWindow="11292" yWindow="204" windowWidth="11028" windowHeight="12036" firstSheet="2" activeTab="2" xr2:uid="{E72E1A8E-89CC-47CA-9DAD-E09CE3761029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/리눅스 기초 디비.xlsx
+++ b/리눅스 기초 디비.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CYWELL\Desktop\linux\minitest\linux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B78BD81-4D3E-4FE3-BE1E-B952E1567954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2FC0BD-38D1-42C2-99FF-2511406CC388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11292" yWindow="204" windowWidth="11028" windowHeight="12036" firstSheet="2" activeTab="2" xr2:uid="{E72E1A8E-89CC-47CA-9DAD-E09CE3761029}"/>
+    <workbookView xWindow="11340" yWindow="216" windowWidth="11028" windowHeight="12036" firstSheet="2" activeTab="2" xr2:uid="{E72E1A8E-89CC-47CA-9DAD-E09CE3761029}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>iptables -j ACCEPT</t>
-  </si>
-  <si>
-    <t>Conntrack</t>
   </si>
   <si>
     <t>ESTABLISHED</t>
@@ -1209,6 +1206,10 @@
   </si>
   <si>
     <t>dw 명령어로 Hello 단어 삭제했다가, u 명령어로 dw 작업 취소해서 Hello world로 복구(|가 커서 위치)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Connection_Tracking</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1690,7 +1691,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1702,7 +1703,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1721,7 +1722,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1809,254 +1810,254 @@
     </row>
     <row r="12" spans="1:5" s="8" customFormat="1">
       <c r="B12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="8" customFormat="1" ht="18" customHeight="1">
       <c r="B13" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="8" customFormat="1">
       <c r="B14" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
         <v>105</v>
       </c>
-      <c r="C15" t="s">
-        <v>106</v>
-      </c>
       <c r="D15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="s">
         <v>107</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>108</v>
-      </c>
-      <c r="D16" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
         <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
         <v>112</v>
-      </c>
-      <c r="C18" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" t="s">
         <v>114</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>115</v>
-      </c>
-      <c r="D19" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" t="s">
         <v>186</v>
       </c>
-      <c r="C25" t="s">
-        <v>187</v>
-      </c>
       <c r="E25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" t="s">
         <v>263</v>
       </c>
-      <c r="B26" t="s">
-        <v>257</v>
-      </c>
-      <c r="C26" t="s">
-        <v>264</v>
-      </c>
       <c r="D26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="8" customFormat="1">
       <c r="B29" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="s">
         <v>172</v>
-      </c>
-      <c r="C31" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="C32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="C34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="B35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" t="s">
         <v>176</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>177</v>
-      </c>
-      <c r="D35" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="B36" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" t="s">
         <v>179</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>180</v>
-      </c>
-      <c r="D36" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D37" t="s">
+        <v>220</v>
+      </c>
+      <c r="E37" t="s">
         <v>221</v>
-      </c>
-      <c r="E37" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B38" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" t="s">
         <v>170</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>171</v>
       </c>
-      <c r="D38" t="s">
-        <v>172</v>
-      </c>
       <c r="E38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2076,200 +2077,200 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1">
       <c r="A2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1">
       <c r="A3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1">
       <c r="A5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1">
       <c r="A6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1">
       <c r="A8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1">
       <c r="A9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1">
       <c r="A11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1">
       <c r="A12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1">
       <c r="A13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1">
       <c r="A14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1">
       <c r="A15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1">
       <c r="A16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B17" t="s">
         <v>269</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>270</v>
-      </c>
-      <c r="C17" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C18" t="s">
         <v>272</v>
-      </c>
-      <c r="C18" t="s">
-        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2292,19 +2293,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="E1" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="34.799999999999997">
@@ -2312,16 +2313,16 @@
         <v>30</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34.799999999999997">
@@ -2329,16 +2330,16 @@
         <v>30</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="E3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2346,16 +2347,16 @@
         <v>30</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2363,16 +2364,16 @@
         <v>30</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="E5" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2380,16 +2381,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="E6" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="26.4">
@@ -2397,16 +2398,16 @@
         <v>30</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2417,13 +2418,13 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2434,13 +2435,13 @@
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2448,16 +2449,16 @@
         <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>52</v>
-      </c>
       <c r="E10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2465,16 +2466,16 @@
         <v>33</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
         <v>53</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="E11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2482,118 +2483,118 @@
         <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="E12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="E14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="E15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="E16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>66</v>
-      </c>
       <c r="E17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="E18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -2618,53 +2619,53 @@
         <v>29</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="69.599999999999994">
       <c r="A2" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34.799999999999997">
       <c r="A3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="34.799999999999997">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="34.799999999999997">
       <c r="A5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2687,7 +2688,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -2699,126 +2700,126 @@
         <v>2</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
         <v>117</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>118</v>
       </c>
-      <c r="D2" t="s">
-        <v>119</v>
-      </c>
       <c r="E2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1">
       <c r="A3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" t="s">
         <v>120</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>121</v>
       </c>
-      <c r="D3" t="s">
-        <v>122</v>
-      </c>
       <c r="E3" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" t="s">
         <v>123</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>124</v>
       </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
       <c r="E4" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1">
       <c r="A5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
         <v>126</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>127</v>
       </c>
-      <c r="D5" t="s">
-        <v>128</v>
-      </c>
       <c r="E5" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" t="s">
         <v>129</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>130</v>
       </c>
-      <c r="D6" t="s">
-        <v>131</v>
-      </c>
       <c r="E6" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" t="s">
         <v>132</v>
       </c>
-      <c r="C7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" t="s">
-        <v>133</v>
-      </c>
       <c r="E7" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" t="s">
         <v>134</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>135</v>
       </c>
-      <c r="D8" t="s">
-        <v>136</v>
-      </c>
       <c r="E8" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1"/>
@@ -2846,206 +2847,206 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>165</v>
-      </c>
       <c r="E1" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" t="s">
         <v>138</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>139</v>
       </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" t="s">
         <v>141</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>142</v>
       </c>
-      <c r="D3" t="s">
-        <v>143</v>
-      </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" t="s">
         <v>144</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>145</v>
       </c>
-      <c r="D4" t="s">
-        <v>146</v>
-      </c>
       <c r="E4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" t="s">
         <v>149</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>150</v>
       </c>
-      <c r="D7" t="s">
-        <v>151</v>
-      </c>
       <c r="E7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" t="s">
         <v>152</v>
       </c>
-      <c r="C8" t="s">
-        <v>153</v>
-      </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" t="s">
         <v>154</v>
       </c>
-      <c r="C9" t="s">
-        <v>155</v>
-      </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" t="s">
         <v>156</v>
       </c>
-      <c r="C10" t="s">
-        <v>157</v>
-      </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" t="s">
         <v>158</v>
       </c>
-      <c r="C11" t="s">
-        <v>159</v>
-      </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
         <v>160</v>
       </c>
-      <c r="C12" t="s">
-        <v>161</v>
-      </c>
       <c r="D12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/리눅스 기초 디비.xlsx
+++ b/리눅스 기초 디비.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CYWELL\Desktop\linux\minitest\linux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2FC0BD-38D1-42C2-99FF-2511406CC388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65564288-EEED-4F8C-8B07-524494B9B36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11340" yWindow="216" windowWidth="11028" windowHeight="12036" firstSheet="2" activeTab="2" xr2:uid="{E72E1A8E-89CC-47CA-9DAD-E09CE3761029}"/>
   </bookViews>
